--- a/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/Final_Methodological_Assessment.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/Final_Methodological_Assessment.xlsx
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Of the 36 station-scale combinations tested, 10 exhibit significant lag-1 autocorrelation (ρ₁ up to 0.5827). Standard MK assumes independence; when positive autocorrelation is present, the MK variance Var(S) is under-estimated, leading to inflated Z statistics and elevated Type I error rates (false positives). MMK corrects Var(S) using the autocorrelation structure of the ranked series (Hamed &amp; Rao 1998). In this dataset, CF ranged 1.000–1.0984, indicating modest but non-negligible inflation. MMK is particularly appropriate here because it preserves Sen's slope exactly (Δ slope = 0 for all 36 rows), modifying only the significance assessment. The 2 significance changes relative to MK represent trends that were borderline-significant (|Z| ≈ 2.1) and whose significance was not robust to autocorrelation correction.</t>
+          <t>Of the 36 station-scale combinations tested, 10 exhibit significant lag-1 autocorrelation (ρ₁ up to 0.5827). Standard MK assumes independence; when positive autocorrelation is present, the MK variance Var(S) is under-estimated, leading to inflated Z statistics and elevated Type I error rates (false positives). MMK corrects Var(S) using the autocorrelation structure of the ranked series (Hamed &amp; Rao 1998). In this dataset, CF ranged 1.000–2.7251, indicating modest but non-negligible inflation. MMK is particularly appropriate here because it preserves Sen's slope exactly (Δ slope = 0 for all 36 rows), modifying only the significance assessment. The 2 significance changes relative to MK represent trends that were borderline-significant (|Z| ≈ 2.1) and whose significance was not robust to autocorrelation correction.</t>
         </is>
       </c>
     </row>
